--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260922.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260922.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>60,628,621</t>
+          <t>8,452,268</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>8,452,268</t>
+          <t>36,106,442</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>36,106,442</t>
+          <t>60,628,621</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1107,17 +1107,17 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>15,474,728</t>
+          <t>29,587,359</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>29,587,359</t>
+          <t>15,474,728</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>87,524,599</t>
+          <t>44,856,084</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>44,856,084</t>
+          <t>87,524,599</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>統一</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>26,214,260</t>
+          <t>113,479,974</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>113,479,974</t>
+          <t>26,214,260</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>202610TX</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>5,747,661</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>5,747,661</t>
+          <t>246,621,807</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>202610TX</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>246,621,807</t>
+          <t>698</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
